--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/30gps/4mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/30gps/4mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.64691652778</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>648.7432087481504</v>
       </c>
-      <c r="W2" t="b">
-        <v>0</v>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
       <c r="X2">
-        <v>648.3263874077096</v>
+        <v>0.251931172</v>
+      </c>
+      <c r="Y2">
+        <v>0.262023614</v>
+      </c>
+      <c r="Z2">
+        <v>0.3634909761175847</v>
+      </c>
+      <c r="AA2">
+        <v>5.046220999999996</v>
+      </c>
+      <c r="AB2">
+        <v>0.07272313438918956</v>
+      </c>
+      <c r="AC2">
+        <v>47.1786395538658</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.64703226852</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>639.5028440238739</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>648.3263874077096</v>
+      </c>
+      <c r="X3">
+        <v>0.25195946</v>
+      </c>
+      <c r="Y3">
+        <v>0.262046534</v>
+      </c>
+      <c r="Z3">
+        <v>0.3635271041681827</v>
+      </c>
+      <c r="AA3">
+        <v>5.043536999999993</v>
+      </c>
+      <c r="AB3">
+        <v>0.07276819887424213</v>
+      </c>
+      <c r="AC3">
+        <v>46.5354701345727</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.64714800926</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>653.7232078256752</v>
       </c>
-      <c r="V4">
-        <v>7.215763735338798</v>
-      </c>
-      <c r="W4" t="b">
-        <v>0</v>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.25197726</v>
+      </c>
+      <c r="Y4">
+        <v>0.262071044</v>
+      </c>
+      <c r="Z4">
+        <v>0.3635571092144363</v>
+      </c>
+      <c r="AA4">
+        <v>5.046892</v>
+      </c>
+      <c r="AB4">
+        <v>0.07272662769555058</v>
+      </c>
+      <c r="AC4">
+        <v>47.54308435147892</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.64726432871</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>648.0618369320678</v>
       </c>
-      <c r="V5">
-        <v>7.159215816613344</v>
-      </c>
-      <c r="W5" t="b">
-        <v>0</v>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>47.08744718727159</v>
+      </c>
+      <c r="X5">
+        <v>0.252001416</v>
+      </c>
+      <c r="Y5">
+        <v>0.262095872</v>
+      </c>
+      <c r="Z5">
+        <v>0.3635917487862527</v>
+      </c>
+      <c r="AA5">
+        <v>5.047227999999997</v>
+      </c>
+      <c r="AB5">
+        <v>0.07272867563378857</v>
+      </c>
+      <c r="AC5">
+        <v>47.13267912886954</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.64738006944</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>645.3325447296619</v>
       </c>
-      <c r="V6">
-        <v>4.279863383954737</v>
-      </c>
-      <c r="W6" t="b">
-        <v>0</v>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>0.252008726</v>
+      </c>
+      <c r="Y6">
+        <v>0.262115608</v>
+      </c>
+      <c r="Z6">
+        <v>0.3636110421004191</v>
+      </c>
+      <c r="AA6">
+        <v>5.053440999999999</v>
+      </c>
+      <c r="AB6">
+        <v>0.07264473169150953</v>
+      </c>
+      <c r="AC6">
+        <v>46.88000956368536</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.64749638889</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>649.4276630179537</v>
       </c>
-      <c r="V7">
-        <v>2.085046387098014</v>
-      </c>
-      <c r="W7" t="b">
+      <c r="V7" t="b">
         <v>1</v>
       </c>
+      <c r="X7">
+        <v>0.25202748</v>
+      </c>
+      <c r="Y7">
+        <v>0.262135344</v>
+      </c>
+      <c r="Z7">
+        <v>0.3636382670307798</v>
+      </c>
+      <c r="AA7">
+        <v>5.053932000000003</v>
+      </c>
+      <c r="AB7">
+        <v>0.07264314343930552</v>
+      </c>
+      <c r="AC7">
+        <v>47.17646687806618</v>
+      </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.64761270834</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>651.0580397522737</v>
       </c>
-      <c r="V8">
-        <v>2.949842237161896</v>
-      </c>
-      <c r="W8" t="b">
+      <c r="V8" t="b">
         <v>1</v>
       </c>
+      <c r="X8">
+        <v>0.25205545</v>
+      </c>
+      <c r="Y8">
+        <v>0.262160174</v>
+      </c>
+      <c r="Z8">
+        <v>0.3636755514279352</v>
+      </c>
+      <c r="AA8">
+        <v>5.052362000000002</v>
+      </c>
+      <c r="AB8">
+        <v>0.07267259867316264</v>
+      </c>
+      <c r="AC8">
+        <v>47.31407963585296</v>
+      </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.64772902778</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>639.9721076939032</v>
       </c>
-      <c r="V9">
-        <v>5.9855874730444</v>
-      </c>
-      <c r="W9" t="b">
-        <v>0</v>
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>0.252079924</v>
+      </c>
+      <c r="Y9">
+        <v>0.262187868</v>
+      </c>
+      <c r="Z9">
+        <v>0.3637124773914571</v>
+      </c>
+      <c r="AA9">
+        <v>5.053971999999995</v>
+      </c>
+      <c r="AB9">
+        <v>0.07265712320040882</v>
+      </c>
+      <c r="AC9">
+        <v>46.49853227354123</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.64784476851</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>652.9932901311315</v>
       </c>
-      <c r="V10">
-        <v>7.026073769601053</v>
-      </c>
-      <c r="W10" t="b">
-        <v>0</v>
+      <c r="V10" t="b">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>0.2520955</v>
+      </c>
+      <c r="Y10">
+        <v>0.262207922</v>
+      </c>
+      <c r="Z10">
+        <v>0.3637377289748867</v>
+      </c>
+      <c r="AA10">
+        <v>5.056210999999998</v>
+      </c>
+      <c r="AB10">
+        <v>0.07263050525411077</v>
+      </c>
+      <c r="AC10">
+        <v>47.42723258976823</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.64796108796</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>649.0169470095038</v>
       </c>
-      <c r="V11">
-        <v>6.672975534816184</v>
-      </c>
-      <c r="W11" t="b">
-        <v>0</v>
+      <c r="V11" t="b">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>0.252107896</v>
+      </c>
+      <c r="Y11">
+        <v>0.262228296</v>
+      </c>
+      <c r="Z11">
+        <v>0.3637610073229543</v>
+      </c>
+      <c r="AA11">
+        <v>5.060200000000002</v>
+      </c>
+      <c r="AB11">
+        <v>0.07257889218429306</v>
+      </c>
+      <c r="AC11">
+        <v>47.10493102278182</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.64807740741</v>
       </c>
@@ -1269,14 +1470,29 @@
       <c r="U12">
         <v>644.5378258575925</v>
       </c>
-      <c r="V12">
-        <v>4.230222748183804</v>
-      </c>
-      <c r="W12" t="b">
-        <v>0</v>
+      <c r="V12" t="b">
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <v>0.252129828</v>
+      </c>
+      <c r="Y12">
+        <v>0.26225026</v>
+      </c>
+      <c r="Z12">
+        <v>0.3637920409208772</v>
+      </c>
+      <c r="AA12">
+        <v>5.060215999999997</v>
+      </c>
+      <c r="AB12">
+        <v>0.07258474142611934</v>
+      </c>
+      <c r="AC12">
+        <v>46.78361142922648</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>46068.64819372685</v>
       </c>
@@ -1340,14 +1556,29 @@
       <c r="U13">
         <v>654.2477846104166</v>
       </c>
-      <c r="V13">
-        <v>4.859826596394957</v>
-      </c>
-      <c r="W13" t="b">
-        <v>0</v>
+      <c r="V13" t="b">
+        <v>1</v>
+      </c>
+      <c r="X13">
+        <v>0.252151124</v>
+      </c>
+      <c r="Y13">
+        <v>0.26226904</v>
+      </c>
+      <c r="Z13">
+        <v>0.3638203384597747</v>
+      </c>
+      <c r="AA13">
+        <v>5.058958000000004</v>
+      </c>
+      <c r="AB13">
+        <v>0.07260798860922112</v>
+      </c>
+      <c r="AC13">
+        <v>47.50361569260128</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:29">
       <c r="A14" s="1">
         <v>46068.64831004629</v>
       </c>
@@ -1411,14 +1642,29 @@
       <c r="U14">
         <v>642.2873955618359</v>
       </c>
-      <c r="V14">
-        <v>6.356081624331847</v>
-      </c>
-      <c r="W14" t="b">
-        <v>0</v>
+      <c r="V14" t="b">
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>0.252158116</v>
+      </c>
+      <c r="Y14">
+        <v>0.262291642</v>
+      </c>
+      <c r="Z14">
+        <v>0.3638414777450829</v>
+      </c>
+      <c r="AA14">
+        <v>5.066762999999995</v>
+      </c>
+      <c r="AB14">
+        <v>0.07250239644393837</v>
+      </c>
+      <c r="AC14">
+        <v>46.56737538396889</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:29">
       <c r="A15" s="1">
         <v>46068.64842578704</v>
       </c>
@@ -1482,14 +1728,29 @@
       <c r="U15">
         <v>657.0266626666706</v>
       </c>
-      <c r="V15">
-        <v>7.831762937259599</v>
-      </c>
-      <c r="W15" t="b">
-        <v>0</v>
+      <c r="V15" t="b">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>0.252186406</v>
+      </c>
+      <c r="Y15">
+        <v>0.262315836</v>
+      </c>
+      <c r="Z15">
+        <v>0.3638785253179634</v>
+      </c>
+      <c r="AA15">
+        <v>5.064715</v>
+      </c>
+      <c r="AB15">
+        <v>0.0725384013407476</v>
+      </c>
+      <c r="AC15">
+        <v>47.65966374808694</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:29">
       <c r="A16" s="1">
         <v>46068.64854152778</v>
       </c>
@@ -1553,14 +1814,29 @@
       <c r="U16">
         <v>646.9346185311659</v>
       </c>
-      <c r="V16">
-        <v>7.535383544179022</v>
-      </c>
-      <c r="W16" t="b">
-        <v>0</v>
+      <c r="V16" t="b">
+        <v>1</v>
+      </c>
+      <c r="X16">
+        <v>0.252205158</v>
+      </c>
+      <c r="Y16">
+        <v>0.26233398</v>
+      </c>
+      <c r="Z16">
+        <v>0.3639046012136221</v>
+      </c>
+      <c r="AA16">
+        <v>5.064411</v>
+      </c>
+      <c r="AB16">
+        <v>0.07254777253279307</v>
+      </c>
+      <c r="AC16">
+        <v>46.93366554878828</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:29">
       <c r="A17" s="1">
         <v>46068.64865726852</v>
       </c>
@@ -1624,11 +1900,26 @@
       <c r="U17">
         <v>650.3562214314784</v>
       </c>
-      <c r="V17">
-        <v>5.132437814407283</v>
-      </c>
-      <c r="W17" t="b">
-        <v>0</v>
+      <c r="V17" t="b">
+        <v>1</v>
+      </c>
+      <c r="X17">
+        <v>0.252227408</v>
+      </c>
+      <c r="Y17">
+        <v>0.262361994</v>
+      </c>
+      <c r="Z17">
+        <v>0.3639402165769187</v>
+      </c>
+      <c r="AA17">
+        <v>5.067292999999999</v>
+      </c>
+      <c r="AB17">
+        <v>0.07251425681357872</v>
+      </c>
+      <c r="AC17">
+        <v>47.16009806119089</v>
       </c>
     </row>
   </sheetData>
